--- a/data/trans_dic/P6901-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,98; 90,87</t>
+          <t>68,83; 91,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,72; 92,14</t>
+          <t>33,54; 91,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,25; 79,62</t>
+          <t>29,14; 77,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,51; 95,47</t>
+          <t>62,08; 95,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,11; 100,0</t>
+          <t>42,89; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,39; 100,0</t>
+          <t>69,59; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,48; 91,6</t>
+          <t>30,48; 92,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,42; 90,85</t>
+          <t>72,18; 90,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,39; 91,23</t>
+          <t>55,99; 91,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,85; 84,78</t>
+          <t>49,27; 85,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,08; 94,85</t>
+          <t>43,64; 94,76</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,8; 79,58</t>
+          <t>64,11; 78,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,78; 84,69</t>
+          <t>67,33; 85,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,34; 89,32</t>
+          <t>71,56; 89,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,17; 92,32</t>
+          <t>66,35; 92,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,13; 83,45</t>
+          <t>63,73; 84,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,89; 87,67</t>
+          <t>66,6; 87,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,88; 97,96</t>
+          <t>81,67; 97,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,05; 77,67</t>
+          <t>51,37; 77,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,75; 78,82</t>
+          <t>66,89; 78,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,78; 83,65</t>
+          <t>70,04; 83,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,14; 90,94</t>
+          <t>78,0; 91,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,37; 83,1</t>
+          <t>62,85; 82,82</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,37; 76,58</t>
+          <t>59,91; 76,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,94; 78,03</t>
+          <t>59,39; 78,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,16; 85,31</t>
+          <t>69,79; 85,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,19; 85,38</t>
+          <t>67,7; 85,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,5; 87,47</t>
+          <t>68,49; 87,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,18; 87,17</t>
+          <t>67,86; 87,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,07; 89,71</t>
+          <t>71,67; 90,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,37; 86,45</t>
+          <t>71,18; 85,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,25; 78,56</t>
+          <t>65,91; 77,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,38; 79,5</t>
+          <t>66,7; 80,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,21; 85,78</t>
+          <t>73,51; 85,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,16; 84,06</t>
+          <t>71,18; 82,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,32; 83,69</t>
+          <t>67,52; 84,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,61; 84,59</t>
+          <t>66,47; 84,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,84; 74,82</t>
+          <t>56,04; 75,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,8; 74,8</t>
+          <t>56,09; 74,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,93; 94,13</t>
+          <t>69,16; 92,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,97; 79,28</t>
+          <t>48,88; 81,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,27; 89,37</t>
+          <t>67,13; 89,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,55; 91,02</t>
+          <t>71,84; 90,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,16; 84,65</t>
+          <t>71,22; 84,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64,39; 81,05</t>
+          <t>65,16; 81,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63,0; 79,69</t>
+          <t>62,68; 78,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,56; 83,47</t>
+          <t>67,77; 84,13</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,63; 96,85</t>
+          <t>78,95; 97,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,09; 85,99</t>
+          <t>58,94; 86,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,34; 90,32</t>
+          <t>64,45; 89,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55,87; 77,37</t>
+          <t>56,11; 78,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,79; 85,87</t>
+          <t>34,36; 85,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,61; 100,0</t>
+          <t>74,75; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,23; 96,37</t>
+          <t>67,24; 96,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,46; 88,89</t>
+          <t>72,79; 88,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,72; 92,37</t>
+          <t>73,56; 93,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70,67; 88,59</t>
+          <t>71,02; 89,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70,82; 90,05</t>
+          <t>70,62; 89,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,9; 80,67</t>
+          <t>66,9; 80,38</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,02; 100,0</t>
+          <t>15,64; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,51; 100,0</t>
+          <t>25,29; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,16; 100,0</t>
+          <t>39,32; 100,0</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,83; 78,8</t>
+          <t>71,04; 78,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69,29; 79,44</t>
+          <t>69,39; 79,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69,64; 79,32</t>
+          <t>69,38; 78,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67,51; 77,89</t>
+          <t>67,47; 77,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,88; 83,08</t>
+          <t>71,9; 83,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,79; 83,76</t>
+          <t>71,63; 83,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,06; 88,9</t>
+          <t>79,65; 89,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>72,4; 84,1</t>
+          <t>72,53; 84,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,42; 79,35</t>
+          <t>72,43; 78,97</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71,98; 79,67</t>
+          <t>71,76; 79,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74,75; 82,01</t>
+          <t>74,66; 81,88</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>71,84; 79,81</t>
+          <t>71,71; 79,64</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31849; 41959</t>
+          <t>31782; 42291</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4309; 9516</t>
+          <t>3463; 9493</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5017; 13655</t>
+          <t>4997; 13344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3818; 5989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12414; 18960</t>
+          <t>12329; 18955</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4536; 10056</t>
+          <t>4314; 10056</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7147; 11643</t>
+          <t>8103; 11643</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3757; 14055</t>
+          <t>4677; 14209</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47818; 59989</t>
+          <t>47664; 59759</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11289; 18595</t>
+          <t>11413; 18613</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13777; 24412</t>
+          <t>14187; 24537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9405; 20233</t>
+          <t>9310; 20215</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90788; 113233</t>
+          <t>91225; 112073</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57621; 73076</t>
+          <t>58096; 73550</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58190; 72861</t>
+          <t>58374; 73032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39088; 54536</t>
+          <t>39195; 54409</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50049; 66153</t>
+          <t>50524; 66644</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43536; 57926</t>
+          <t>44004; 58021</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36977; 45347</t>
+          <t>37806; 45346</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25001; 38797</t>
+          <t>25661; 38669</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>147894; 174648</t>
+          <t>148204; 174363</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106322; 127444</t>
+          <t>106715; 127610</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99909; 116280</t>
+          <t>99731; 116437</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69086; 90595</t>
+          <t>68516; 90289</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76083; 96509</t>
+          <t>75508; 95807</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56709; 76375</t>
+          <t>58125; 77302</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78236; 96505</t>
+          <t>78949; 96149</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64184; 81562</t>
+          <t>64679; 81424</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47282; 61266</t>
+          <t>47968; 61375</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49518; 63310</t>
+          <t>49284; 63432</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51498; 64108</t>
+          <t>51212; 64670</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53163; 65317</t>
+          <t>53779; 64940</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>127945; 154028</t>
+          <t>129224; 152834</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113177; 135560</t>
+          <t>113721; 137298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135132; 158341</t>
+          <t>135684; 156888</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>121749; 143820</t>
+          <t>121773; 141724</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74796; 92992</t>
+          <t>75021; 93895</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59162; 76269</t>
+          <t>59937; 76425</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49226; 68406</t>
+          <t>51237; 69429</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60570; 81193</t>
+          <t>60883; 81300</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25158; 34863</t>
+          <t>25614; 34163</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20150; 31965</t>
+          <t>19710; 32812</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38305; 50141</t>
+          <t>37667; 50073</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110871; 141036</t>
+          <t>111323; 140674</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103939; 125400</t>
+          <t>105505; 125359</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84023; 105754</t>
+          <t>85028; 106852</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92943; 117563</t>
+          <t>92476; 116433</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>178025; 219953</t>
+          <t>178573; 221680</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35620; 44437</t>
+          <t>36224; 44923</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25777; 36886</t>
+          <t>25283; 37003</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28409; 40508</t>
+          <t>28905; 40357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37675; 52176</t>
+          <t>37836; 52873</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4979; 11943</t>
+          <t>4779; 11929</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18094; 24582</t>
+          <t>18374; 24582</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20706; 29682</t>
+          <t>20710; 29664</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40775; 49341</t>
+          <t>40406; 49245</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44078; 55232</t>
+          <t>43981; 55792</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47689; 59780</t>
+          <t>47923; 60098</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53575; 68121</t>
+          <t>53418; 67811</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82250; 99178</t>
+          <t>82253; 98820</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>381; 2923</t>
+          <t>457; 2923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>772; 2914</t>
+          <t>737; 2914</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2635; 5836</t>
+          <t>2295; 5836</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>334550; 372165</t>
+          <t>335509; 372213</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>226963; 260196</t>
+          <t>227282; 259495</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>243733; 277615</t>
+          <t>242826; 274945</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>229201; 264426</t>
+          <t>229067; 262543</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>158216; 182869</t>
+          <t>158264; 183829</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>153383; 178952</t>
+          <t>153048; 177544</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>171011; 192299</t>
+          <t>172284; 193490</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>256445; 297888</t>
+          <t>256929; 297664</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>501482; 549421</t>
+          <t>501537; 546815</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>389548; 431185</t>
+          <t>388400; 429377</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>423295; 464402</t>
+          <t>422810; 463700</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>498342; 553674</t>
+          <t>497433; 552447</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6901-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,83; 91,59</t>
+          <t>67,87; 90,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,54; 91,93</t>
+          <t>38,07; 91,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,14; 77,8</t>
+          <t>29,35; 79,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,08; 95,45</t>
+          <t>66,3; 95,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,89; 100,0</t>
+          <t>49,11; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,59; 100,0</t>
+          <t>69,0; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,48; 92,6</t>
+          <t>30,73; 92,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,18; 90,5</t>
+          <t>73,15; 91,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,99; 91,31</t>
+          <t>55,66; 91,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,27; 85,21</t>
+          <t>52,11; 85,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,64; 94,76</t>
+          <t>50,42; 95,96</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,11; 78,76</t>
+          <t>62,36; 79,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,33; 85,24</t>
+          <t>65,96; 84,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,56; 89,53</t>
+          <t>70,85; 88,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,35; 92,1</t>
+          <t>71,36; 93,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,73; 84,07</t>
+          <t>63,86; 84,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,6; 87,82</t>
+          <t>67,96; 88,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,67; 97,96</t>
+          <t>81,5; 97,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,37; 77,42</t>
+          <t>50,02; 78,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,89; 78,7</t>
+          <t>66,44; 78,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,04; 83,76</t>
+          <t>70,15; 84,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,0; 91,06</t>
+          <t>77,85; 90,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,85; 82,82</t>
+          <t>66,69; 84,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,91; 76,02</t>
+          <t>60,34; 76,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,39; 78,98</t>
+          <t>60,11; 78,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,79; 85,0</t>
+          <t>69,4; 85,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,7; 85,23</t>
+          <t>67,64; 84,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,49; 87,63</t>
+          <t>68,05; 87,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,86; 87,34</t>
+          <t>65,73; 86,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,67; 90,5</t>
+          <t>71,79; 90,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,18; 85,95</t>
+          <t>71,66; 86,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,91; 77,95</t>
+          <t>66,07; 79,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,7; 80,52</t>
+          <t>66,77; 80,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,51; 85,0</t>
+          <t>73,71; 85,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,18; 82,84</t>
+          <t>71,06; 83,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,52; 84,51</t>
+          <t>68,52; 83,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,47; 84,76</t>
+          <t>66,31; 85,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,04; 75,94</t>
+          <t>55,27; 75,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,09; 74,89</t>
+          <t>59,16; 76,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,16; 92,24</t>
+          <t>68,64; 92,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,88; 81,38</t>
+          <t>48,96; 79,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,13; 89,25</t>
+          <t>67,0; 89,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,84; 90,79</t>
+          <t>74,15; 85,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,22; 84,62</t>
+          <t>71,22; 84,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,16; 81,89</t>
+          <t>64,43; 80,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,68; 78,92</t>
+          <t>62,76; 78,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,77; 84,13</t>
+          <t>69,43; 79,5</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,95; 97,91</t>
+          <t>78,87; 97,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,94; 86,26</t>
+          <t>60,09; 86,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,45; 89,99</t>
+          <t>65,0; 90,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56,11; 78,4</t>
+          <t>57,37; 78,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,36; 85,76</t>
+          <t>36,22; 86,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,75; 100,0</t>
+          <t>74,13; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,24; 96,32</t>
+          <t>69,62; 96,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>72,79; 88,72</t>
+          <t>73,01; 88,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,56; 93,31</t>
+          <t>74,14; 92,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,02; 89,06</t>
+          <t>70,11; 89,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70,62; 89,64</t>
+          <t>70,96; 89,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,9; 80,38</t>
+          <t>66,8; 80,78</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,64; 100,0</t>
+          <t>17,13; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,29; 100,0</t>
+          <t>28,99; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,32; 100,0</t>
+          <t>43,85; 100,0</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>71,04; 78,81</t>
+          <t>70,82; 79,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69,39; 79,22</t>
+          <t>69,03; 78,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69,38; 78,56</t>
+          <t>69,24; 79,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67,47; 77,33</t>
+          <t>69,95; 79,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,9; 83,51</t>
+          <t>72,29; 83,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,63; 83,1</t>
+          <t>70,59; 83,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,65; 89,46</t>
+          <t>79,3; 89,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>72,53; 84,03</t>
+          <t>73,44; 81,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,43; 78,97</t>
+          <t>72,44; 79,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71,76; 79,34</t>
+          <t>71,93; 79,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74,66; 81,88</t>
+          <t>75,14; 82,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>71,71; 79,64</t>
+          <t>72,95; 79,26</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>20398</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31782; 42291</t>
+          <t>31335; 41764</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3463; 9493</t>
+          <t>3932; 9492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4997; 13344</t>
+          <t>5034; 13665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12329; 18955</t>
+          <t>13166; 18965</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4314; 10056</t>
+          <t>4939; 10056</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8103; 11643</t>
+          <t>8034; 11643</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4677; 14209</t>
+          <t>4887; 14779</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47664; 59759</t>
+          <t>48304; 60329</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11413; 18613</t>
+          <t>11346; 18634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14187; 24537</t>
+          <t>15004; 24532</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9310; 20215</t>
+          <t>12665; 24102</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48645</t>
+          <t>59104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31980</t>
+          <t>33420</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80625</t>
+          <t>92524</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91225; 112073</t>
+          <t>88729; 113040</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58096; 73550</t>
+          <t>56917; 73174</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58374; 73032</t>
+          <t>57797; 72445</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39195; 54409</t>
+          <t>49660; 65252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50524; 66644</t>
+          <t>50624; 66759</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44004; 58021</t>
+          <t>44903; 58266</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37806; 45346</t>
+          <t>37729; 45332</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25661; 38669</t>
+          <t>25766; 40344</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>148204; 174363</t>
+          <t>147198; 174347</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106715; 127610</t>
+          <t>106884; 128011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99731; 116437</t>
+          <t>99542; 116019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68516; 90289</t>
+          <t>80763; 102237</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73275</t>
+          <t>85418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59674</t>
+          <t>68894</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>132950</t>
+          <t>154312</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75508; 95807</t>
+          <t>76046; 96058</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58125; 77302</t>
+          <t>58837; 76845</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78949; 96149</t>
+          <t>78504; 96234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64679; 81424</t>
+          <t>74387; 93459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47968; 61375</t>
+          <t>47663; 61284</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49284; 63432</t>
+          <t>47741; 62899</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51212; 64670</t>
+          <t>51299; 64863</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53779; 64940</t>
+          <t>62085; 74810</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>129224; 152834</t>
+          <t>129551; 155123</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113721; 137298</t>
+          <t>113847; 137111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135684; 156888</t>
+          <t>136058; 157498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>121773; 141724</t>
+          <t>139718; 163665</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71313</t>
+          <t>82487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>126586</t>
+          <t>101694</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>197899</t>
+          <t>184182</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75021; 93895</t>
+          <t>76131; 93284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59937; 76425</t>
+          <t>59786; 77054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51237; 69429</t>
+          <t>50531; 68674</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60883; 81300</t>
+          <t>71301; 91890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25614; 34163</t>
+          <t>25423; 34109</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19710; 32812</t>
+          <t>19742; 32161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37667; 50073</t>
+          <t>37593; 50037</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>111323; 140674</t>
+          <t>93806; 108517</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>105505; 125359</t>
+          <t>105507; 125788</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85028; 106852</t>
+          <t>84069; 104998</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92476; 116433</t>
+          <t>92593; 115857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>178573; 221680</t>
+          <t>171516; 196389</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45575</t>
+          <t>49173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90971</t>
+          <t>99388</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36224; 44923</t>
+          <t>36188; 44906</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25283; 37003</t>
+          <t>25777; 36975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28905; 40357</t>
+          <t>29151; 40365</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37836; 52873</t>
+          <t>41323; 56635</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4779; 11929</t>
+          <t>5038; 11976</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18374; 24582</t>
+          <t>18223; 24582</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20710; 29664</t>
+          <t>21444; 29698</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40406; 49245</t>
+          <t>45098; 54397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43981; 55792</t>
+          <t>44327; 55016</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47923; 60098</t>
+          <t>47308; 60501</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53418; 67811</t>
+          <t>53677; 67926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82253; 98820</t>
+          <t>89372; 108073</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>5225</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>457; 2923</t>
+          <t>628; 3668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>737; 2914</t>
+          <t>869; 2999</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2295; 5836</t>
+          <t>2924; 6667</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>246977</t>
+          <t>288195</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>276261</t>
+          <t>267835</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>523238</t>
+          <t>556030</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>335509; 372213</t>
+          <t>334494; 373635</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>227282; 259495</t>
+          <t>226127; 258741</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>242826; 274945</t>
+          <t>242356; 277379</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>229067; 262543</t>
+          <t>269317; 304522</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>158264; 183829</t>
+          <t>159126; 183386</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>153048; 177544</t>
+          <t>150830; 178059</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>172284; 193490</t>
+          <t>171528; 194382</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>256929; 297664</t>
+          <t>253612; 280893</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>501537; 546815</t>
+          <t>501604; 547366</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>388400; 429377</t>
+          <t>389279; 428998</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>422810; 463700</t>
+          <t>425538; 464599</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>497433; 552447</t>
+          <t>532766; 578889</t>
         </is>
       </c>
     </row>
